--- a/data/xlsx/sbce_config_kvm_sbcems_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_sbcems_template.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">ovf</t>
   </si>
   <si>
-    <t xml:space="preserve">/home/custadm/sbce-10.2.0.0-86-24077.qcow2</t>
+    <t xml:space="preserve">/home/custadm/sbce-10.2.1.0-101-24795.qcow2</t>
   </si>
   <si>
     <t xml:space="preserve">Path to OVA</t>
